--- a/artfynd/A 39741-2023 artfynd.xlsx
+++ b/artfynd/A 39741-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114842257</v>
+        <v>132279024</v>
       </c>
       <c r="B2" t="n">
-        <v>57425</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58519</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,18 +703,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Enstalund (Enstalund), Upl</t>
+          <t>enstalund 514, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>647925</v>
+        <v>647853</v>
       </c>
       <c r="R2" t="n">
-        <v>6646210</v>
+        <v>6646217</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -746,12 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,6 +777,419 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>114842257</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Enstalund, Enstalund, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>647925</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6646210</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-02-24</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-02-24</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Vallgårda</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Vallgårda</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132278259</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58134</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>enstalund 514, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>647853</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6646217</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Vallgårda</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Vallgårda</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132278468</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58596</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>enstalund 514, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>647853</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6646217</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Vallgårda</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Vallgårda</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132278298</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>enstalund 514, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>647853</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6646217</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Vallgårda</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Vallgårda</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
